--- a/docentes/Flores Ovalle Victor - Estadisticos 20241.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>JARET</t>
   </si>
 </sst>
 </file>
@@ -562,16 +571,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -585,16 +597,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>89.29000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -659,7 +674,7 @@
         <v>84</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -685,7 +700,7 @@
         <v>89.29000000000001</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -695,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -725,6 +740,29 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920357</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20241.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -76,7 +76,13 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
   </si>
   <si>
     <t>JARET</t>
@@ -710,7 +716,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -742,7 +748,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920357</v>
+        <v>23330051920236</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -751,15 +757,38 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920357</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20241.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -73,13 +73,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
   </si>
   <si>
     <t>EDUARDO</t>
@@ -716,7 +731,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -748,16 +763,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920236</v>
+        <v>23330051920271</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -766,21 +781,21 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920357</v>
+        <v>22330051920239</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -789,6 +804,52 @@
         <v>11</v>
       </c>
       <c r="G3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920236</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920357</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20241.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20241.xlsx
@@ -85,22 +85,22 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>FERNANDA YAMILET</t>
   </si>
   <si>
     <t>CRHIS AMINADAB</t>
   </si>
   <si>
+    <t>JARET</t>
+  </si>
+  <si>
     <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JARET</t>
   </si>
 </sst>
 </file>
@@ -804,12 +804,12 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920236</v>
+        <v>22330051920357</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -821,10 +821,10 @@
         <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920357</v>
+        <v>23330051920236</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -844,13 +844,13 @@
         <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores Ovalle Victor - Estadisticos 20241.xlsx
+++ b/docentes/Flores Ovalle Victor - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,34 +73,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>FERNANDA YAMILET</t>
-  </si>
-  <si>
     <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
   </si>
 </sst>
 </file>
@@ -686,16 +665,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -712,13 +691,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>89.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
         <v>7.6</v>
@@ -731,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -763,94 +742,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920271</v>
+        <v>22330051920239</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920239</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920357</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920236</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
